--- a/FORMATO PARA 2.º a 7.º EGB.xlsx
+++ b/FORMATO PARA 2.º a 7.º EGB.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D27B0CF-7792-46CB-A1EC-C6C877B542F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A81B4EE1-D2D0-4B16-801E-B3D790684856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="66">
   <si>
     <t>UNIDAD EDUCATIVA EMILIANO HINOSTROZA</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+  </si>
+  <si>
+    <t>EVALUACIÓN COMPORTAMENTAL</t>
   </si>
 </sst>
 </file>
@@ -232,7 +235,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000000000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,8 +269,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -284,8 +301,14 @@
         <fgColor rgb="FFA9A9A9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA9A9A9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -308,11 +331,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -331,6 +367,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -671,7 +713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE49"/>
+  <dimension ref="A1:AD49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.21875" customWidth="1"/>
@@ -680,6 +722,7 @@
     <col min="4" max="4" width="34.33203125" customWidth="1"/>
     <col min="5" max="10" width="30" customWidth="1"/>
     <col min="11" max="11" width="40" customWidth="1"/>
+    <col min="12" max="12" width="34.21875" customWidth="1"/>
     <col min="20" max="20" width="0" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="39.21875" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="33.21875" hidden="1" customWidth="1"/>
@@ -887,6 +930,9 @@
       <c r="K9" s="2" t="s">
         <v>64</v>
       </c>
+      <c r="L9" s="9" t="s">
+        <v>65</v>
+      </c>
       <c r="U9" t="s">
         <v>59</v>
       </c>
@@ -909,6 +955,7 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
+      <c r="L10" s="10"/>
       <c r="V10" t="s">
         <v>41</v>
       </c>
@@ -928,6 +975,7 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
+      <c r="L11" s="10"/>
       <c r="V11" t="s">
         <v>42</v>
       </c>
@@ -947,6 +995,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
+      <c r="L12" s="10"/>
       <c r="V12" t="s">
         <v>43</v>
       </c>
@@ -966,6 +1015,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
+      <c r="L13" s="10"/>
       <c r="V13" t="s">
         <v>44</v>
       </c>
@@ -985,6 +1035,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
+      <c r="L14" s="10"/>
       <c r="V14" t="s">
         <v>45</v>
       </c>
@@ -1004,6 +1055,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
+      <c r="L15" s="10"/>
       <c r="V15" t="s">
         <v>46</v>
       </c>
@@ -1020,6 +1072,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
+      <c r="L16" s="10"/>
       <c r="V16" t="s">
         <v>47</v>
       </c>
@@ -1036,6 +1089,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
+      <c r="L17" s="10"/>
       <c r="V17" t="s">
         <v>42</v>
       </c>
@@ -1055,6 +1109,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
+      <c r="L18" s="10"/>
       <c r="V18" t="s">
         <v>43</v>
       </c>
@@ -1074,6 +1129,7 @@
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
+      <c r="L19" s="10"/>
       <c r="V19" t="s">
         <v>44</v>
       </c>
@@ -1093,6 +1149,7 @@
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
+      <c r="L20" s="10"/>
       <c r="V20" t="s">
         <v>45</v>
       </c>
@@ -1112,6 +1169,7 @@
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
+      <c r="L21" s="10"/>
       <c r="V21" t="s">
         <v>46</v>
       </c>
@@ -1128,6 +1186,7 @@
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
+      <c r="L22" s="10"/>
       <c r="V22" t="s">
         <v>47</v>
       </c>
@@ -1144,6 +1203,7 @@
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
+      <c r="L23" s="10"/>
       <c r="V23" t="s">
         <v>42</v>
       </c>
@@ -1163,6 +1223,7 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
+      <c r="L24" s="10"/>
       <c r="V24" t="s">
         <v>43</v>
       </c>
@@ -1182,6 +1243,7 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
+      <c r="L25" s="10"/>
       <c r="V25" t="s">
         <v>44</v>
       </c>
@@ -1201,6 +1263,7 @@
       <c r="I26" s="3"/>
       <c r="J26" s="3"/>
       <c r="K26" s="3"/>
+      <c r="L26" s="10"/>
       <c r="V26" t="s">
         <v>45</v>
       </c>
@@ -1220,6 +1283,7 @@
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
+      <c r="L27" s="10"/>
       <c r="V27" t="s">
         <v>46</v>
       </c>
@@ -1236,6 +1300,7 @@
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
+      <c r="L28" s="10"/>
       <c r="V28" t="s">
         <v>47</v>
       </c>
@@ -1252,6 +1317,7 @@
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
+      <c r="L29" s="10"/>
       <c r="V29" t="s">
         <v>42</v>
       </c>
@@ -1271,6 +1337,7 @@
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
+      <c r="L30" s="10"/>
       <c r="V30" t="s">
         <v>43</v>
       </c>
@@ -1290,6 +1357,7 @@
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
+      <c r="L31" s="10"/>
       <c r="V31" t="s">
         <v>44</v>
       </c>
@@ -1309,6 +1377,7 @@
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
+      <c r="L32" s="10"/>
       <c r="V32" t="s">
         <v>45</v>
       </c>
@@ -1328,6 +1397,7 @@
       <c r="I33" s="3"/>
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
+      <c r="L33" s="10"/>
       <c r="V33" t="s">
         <v>46</v>
       </c>
@@ -1344,6 +1414,7 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
+      <c r="L34" s="10"/>
       <c r="V34" t="s">
         <v>47</v>
       </c>
